--- a/Data/European Earnings Index.xlsx
+++ b/Data/European Earnings Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\european-average-earnings-index\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C550CD-2131-4BF8-A56A-1E683FF347D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4566196B-4094-4723-9455-599633B3F159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -173,10 +173,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -186,13 +187,13 @@
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -213,12 +214,12 @@
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{CB4AD6FB-72D6-498E-A9AD-12A465F0FBC2}" name="country"/>
     <tableColumn id="2" xr3:uid="{99E049E3-6CCE-4AFB-8FFC-0C279DC89557}" name="date"/>
-    <tableColumn id="3" xr3:uid="{4D95BB70-7F43-4895-B2D4-08D9A6AA4319}" name="price_level_index" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{7142205F-B21D-4A7A-8E0C-A302B67BB538}" name="annual_net_earnings" dataDxfId="0"/>
-    <tableColumn id="8" xr3:uid="{560F4622-03CE-4B2D-9B44-80296AFFDF06}" name="european_earnings_index" dataDxfId="1">
+    <tableColumn id="3" xr3:uid="{4D95BB70-7F43-4895-B2D4-08D9A6AA4319}" name="price_level_index" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{7142205F-B21D-4A7A-8E0C-A302B67BB538}" name="annual_net_earnings" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{560F4622-03CE-4B2D-9B44-80296AFFDF06}" name="european_earnings_index" dataDxfId="2">
       <calculatedColumnFormula>Table1[[#This Row],[annual_net_earnings]]*(1+(100-Table1[[#This Row],[price_level_index]])/100)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{D4D1ED1B-E2C5-4AB4-9F95-3A21FF9D2EB7}" name="yoy" dataDxfId="3">
+    <tableColumn id="9" xr3:uid="{D4D1ED1B-E2C5-4AB4-9F95-3A21FF9D2EB7}" name="yoy" dataDxfId="1">
       <calculatedColumnFormula>IF(B2&gt;B1,(Table1[[#This Row],[european_earnings_index]]-E1)/E1,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -493,6 +494,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" style="1" customWidth="1"/>
     <col min="4" max="4" width="21.7109375" customWidth="1"/>
     <col min="5" max="5" width="26.28515625" customWidth="1"/>
@@ -523,8 +525,8 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2">
-        <v>2014</v>
+      <c r="B2" s="3">
+        <v>41640</v>
       </c>
       <c r="C2" s="1">
         <v>113.7</v>
@@ -545,8 +547,8 @@
       <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="B3">
-        <v>2015</v>
+      <c r="B3" s="3">
+        <v>42005</v>
       </c>
       <c r="C3" s="1">
         <v>114.1</v>
@@ -567,8 +569,8 @@
       <c r="A4" t="s">
         <v>0</v>
       </c>
-      <c r="B4">
-        <v>2016</v>
+      <c r="B4" s="3">
+        <v>42370</v>
       </c>
       <c r="C4" s="1">
         <v>115.2</v>
@@ -589,8 +591,8 @@
       <c r="A5" t="s">
         <v>0</v>
       </c>
-      <c r="B5">
-        <v>2017</v>
+      <c r="B5" s="3">
+        <v>42736</v>
       </c>
       <c r="C5" s="1">
         <v>116.5</v>
@@ -611,8 +613,8 @@
       <c r="A6" t="s">
         <v>0</v>
       </c>
-      <c r="B6">
-        <v>2018</v>
+      <c r="B6" s="3">
+        <v>43101</v>
       </c>
       <c r="C6" s="1">
         <v>117.2</v>
@@ -633,8 +635,8 @@
       <c r="A7" t="s">
         <v>0</v>
       </c>
-      <c r="B7">
-        <v>2019</v>
+      <c r="B7" s="3">
+        <v>43466</v>
       </c>
       <c r="C7" s="1">
         <v>118.3</v>
@@ -655,8 +657,8 @@
       <c r="A8" t="s">
         <v>0</v>
       </c>
-      <c r="B8">
-        <v>2020</v>
+      <c r="B8" s="3">
+        <v>43831</v>
       </c>
       <c r="C8" s="1">
         <v>118.7</v>
@@ -677,8 +679,8 @@
       <c r="A9" t="s">
         <v>0</v>
       </c>
-      <c r="B9">
-        <v>2021</v>
+      <c r="B9" s="3">
+        <v>44197</v>
       </c>
       <c r="C9" s="1">
         <v>117.6</v>
@@ -699,8 +701,8 @@
       <c r="A10" t="s">
         <v>0</v>
       </c>
-      <c r="B10">
-        <v>2022</v>
+      <c r="B10" s="3">
+        <v>44562</v>
       </c>
       <c r="C10" s="1">
         <v>118.2</v>
@@ -721,8 +723,8 @@
       <c r="A11" t="s">
         <v>1</v>
       </c>
-      <c r="B11">
-        <v>2014</v>
+      <c r="B11" s="3">
+        <v>41640</v>
       </c>
       <c r="C11" s="1">
         <v>113.5</v>
@@ -743,8 +745,8 @@
       <c r="A12" t="s">
         <v>1</v>
       </c>
-      <c r="B12">
-        <v>2015</v>
+      <c r="B12" s="3">
+        <v>42005</v>
       </c>
       <c r="C12" s="1">
         <v>113.1</v>
@@ -765,8 +767,8 @@
       <c r="A13" t="s">
         <v>1</v>
       </c>
-      <c r="B13">
-        <v>2016</v>
+      <c r="B13" s="3">
+        <v>42370</v>
       </c>
       <c r="C13" s="1">
         <v>115.4</v>
@@ -787,8 +789,8 @@
       <c r="A14" t="s">
         <v>1</v>
       </c>
-      <c r="B14">
-        <v>2017</v>
+      <c r="B14" s="3">
+        <v>42736</v>
       </c>
       <c r="C14" s="1">
         <v>116.7</v>
@@ -809,8 +811,8 @@
       <c r="A15" t="s">
         <v>1</v>
       </c>
-      <c r="B15">
-        <v>2018</v>
+      <c r="B15" s="3">
+        <v>43101</v>
       </c>
       <c r="C15" s="1">
         <v>117.2</v>
@@ -831,8 +833,8 @@
       <c r="A16" t="s">
         <v>1</v>
       </c>
-      <c r="B16">
-        <v>2019</v>
+      <c r="B16" s="3">
+        <v>43466</v>
       </c>
       <c r="C16" s="1">
         <v>117.2</v>
@@ -853,8 +855,8 @@
       <c r="A17" t="s">
         <v>1</v>
       </c>
-      <c r="B17">
-        <v>2020</v>
+      <c r="B17" s="3">
+        <v>43831</v>
       </c>
       <c r="C17" s="1">
         <v>115.6</v>
@@ -875,8 +877,8 @@
       <c r="A18" t="s">
         <v>1</v>
       </c>
-      <c r="B18">
-        <v>2021</v>
+      <c r="B18" s="3">
+        <v>44197</v>
       </c>
       <c r="C18" s="1">
         <v>114.9</v>
@@ -897,8 +899,8 @@
       <c r="A19" t="s">
         <v>1</v>
       </c>
-      <c r="B19">
-        <v>2022</v>
+      <c r="B19" s="3">
+        <v>44562</v>
       </c>
       <c r="C19" s="1">
         <v>115.90000000000002</v>
@@ -919,8 +921,8 @@
       <c r="A20" t="s">
         <v>2</v>
       </c>
-      <c r="B20">
-        <v>2014</v>
+      <c r="B20" s="3">
+        <v>41640</v>
       </c>
       <c r="C20" s="1">
         <v>44.4</v>
@@ -941,8 +943,8 @@
       <c r="A21" t="s">
         <v>2</v>
       </c>
-      <c r="B21">
-        <v>2015</v>
+      <c r="B21" s="3">
+        <v>42005</v>
       </c>
       <c r="C21" s="1">
         <v>44.8</v>
@@ -963,8 +965,8 @@
       <c r="A22" t="s">
         <v>2</v>
       </c>
-      <c r="B22">
-        <v>2016</v>
+      <c r="B22" s="3">
+        <v>42370</v>
       </c>
       <c r="C22" s="1">
         <v>45.1</v>
@@ -985,8 +987,8 @@
       <c r="A23" t="s">
         <v>2</v>
       </c>
-      <c r="B23">
-        <v>2017</v>
+      <c r="B23" s="3">
+        <v>42736</v>
       </c>
       <c r="C23" s="1">
         <v>46.7</v>
@@ -1007,8 +1009,8 @@
       <c r="A24" t="s">
         <v>2</v>
       </c>
-      <c r="B24">
-        <v>2018</v>
+      <c r="B24" s="3">
+        <v>43101</v>
       </c>
       <c r="C24" s="1">
         <v>47.6</v>
@@ -1029,8 +1031,8 @@
       <c r="A25" t="s">
         <v>2</v>
       </c>
-      <c r="B25">
-        <v>2019</v>
+      <c r="B25" s="3">
+        <v>43466</v>
       </c>
       <c r="C25" s="1">
         <v>49.5</v>
@@ -1051,8 +1053,8 @@
       <c r="A26" t="s">
         <v>2</v>
       </c>
-      <c r="B26">
-        <v>2020</v>
+      <c r="B26" s="3">
+        <v>43831</v>
       </c>
       <c r="C26" s="1">
         <v>50.8</v>
@@ -1073,8 +1075,8 @@
       <c r="A27" t="s">
         <v>2</v>
       </c>
-      <c r="B27">
-        <v>2021</v>
+      <c r="B27" s="3">
+        <v>44197</v>
       </c>
       <c r="C27" s="1">
         <v>51.8</v>
@@ -1095,8 +1097,8 @@
       <c r="A28" t="s">
         <v>2</v>
       </c>
-      <c r="B28">
-        <v>2022</v>
+      <c r="B28" s="3">
+        <v>44562</v>
       </c>
       <c r="C28" s="1">
         <v>50.699999999999996</v>
@@ -1117,8 +1119,8 @@
       <c r="A29" t="s">
         <v>3</v>
       </c>
-      <c r="B29">
-        <v>2014</v>
+      <c r="B29" s="3">
+        <v>41640</v>
       </c>
       <c r="C29" s="1">
         <v>65.099999999999994</v>
@@ -1139,8 +1141,8 @@
       <c r="A30" t="s">
         <v>3</v>
       </c>
-      <c r="B30">
-        <v>2015</v>
+      <c r="B30" s="3">
+        <v>42005</v>
       </c>
       <c r="C30" s="1">
         <v>64.5</v>
@@ -1161,8 +1163,8 @@
       <c r="A31" t="s">
         <v>3</v>
       </c>
-      <c r="B31">
-        <v>2016</v>
+      <c r="B31" s="3">
+        <v>42370</v>
       </c>
       <c r="C31" s="1">
         <v>64.3</v>
@@ -1183,8 +1185,8 @@
       <c r="A32" t="s">
         <v>3</v>
       </c>
-      <c r="B32">
-        <v>2017</v>
+      <c r="B32" s="3">
+        <v>42736</v>
       </c>
       <c r="C32" s="1">
         <v>64.900000000000006</v>
@@ -1205,8 +1207,8 @@
       <c r="A33" t="s">
         <v>3</v>
       </c>
-      <c r="B33">
-        <v>2018</v>
+      <c r="B33" s="3">
+        <v>43101</v>
       </c>
       <c r="C33" s="1">
         <v>66.3</v>
@@ -1227,8 +1229,8 @@
       <c r="A34" t="s">
         <v>3</v>
       </c>
-      <c r="B34">
-        <v>2019</v>
+      <c r="B34" s="3">
+        <v>43466</v>
       </c>
       <c r="C34" s="1">
         <v>67</v>
@@ -1249,8 +1251,8 @@
       <c r="A35" t="s">
         <v>3</v>
       </c>
-      <c r="B35">
-        <v>2020</v>
+      <c r="B35" s="3">
+        <v>43831</v>
       </c>
       <c r="C35" s="1">
         <v>66</v>
@@ -1271,8 +1273,8 @@
       <c r="A36" t="s">
         <v>3</v>
       </c>
-      <c r="B36">
-        <v>2021</v>
+      <c r="B36" s="3">
+        <v>44197</v>
       </c>
       <c r="C36" s="1">
         <v>66.900000000000006</v>
@@ -1293,8 +1295,8 @@
       <c r="A37" t="s">
         <v>3</v>
       </c>
-      <c r="B37">
-        <v>2022</v>
+      <c r="B37" s="3">
+        <v>44562</v>
       </c>
       <c r="C37" s="1">
         <v>66.63333333333334</v>
@@ -1315,8 +1317,8 @@
       <c r="A38" t="s">
         <v>4</v>
       </c>
-      <c r="B38">
-        <v>2014</v>
+      <c r="B38" s="3">
+        <v>41640</v>
       </c>
       <c r="C38" s="1">
         <v>95.8</v>
@@ -1337,8 +1339,8 @@
       <c r="A39" t="s">
         <v>4</v>
       </c>
-      <c r="B39">
-        <v>2015</v>
+      <c r="B39" s="3">
+        <v>42005</v>
       </c>
       <c r="C39" s="1">
         <v>94.2</v>
@@ -1359,8 +1361,8 @@
       <c r="A40" t="s">
         <v>4</v>
       </c>
-      <c r="B40">
-        <v>2016</v>
+      <c r="B40" s="3">
+        <v>42370</v>
       </c>
       <c r="C40" s="1">
         <v>91.7</v>
@@ -1381,8 +1383,8 @@
       <c r="A41" t="s">
         <v>4</v>
       </c>
-      <c r="B41">
-        <v>2017</v>
+      <c r="B41" s="3">
+        <v>42736</v>
       </c>
       <c r="C41" s="1">
         <v>92</v>
@@ -1403,8 +1405,8 @@
       <c r="A42" t="s">
         <v>4</v>
       </c>
-      <c r="B42">
-        <v>2018</v>
+      <c r="B42" s="3">
+        <v>43101</v>
       </c>
       <c r="C42" s="1">
         <v>93.2</v>
@@ -1425,8 +1427,8 @@
       <c r="A43" t="s">
         <v>4</v>
       </c>
-      <c r="B43">
-        <v>2019</v>
+      <c r="B43" s="3">
+        <v>43466</v>
       </c>
       <c r="C43" s="1">
         <v>93.9</v>
@@ -1447,8 +1449,8 @@
       <c r="A44" t="s">
         <v>4</v>
       </c>
-      <c r="B44">
-        <v>2020</v>
+      <c r="B44" s="3">
+        <v>43831</v>
       </c>
       <c r="C44" s="1">
         <v>93.7</v>
@@ -1469,8 +1471,8 @@
       <c r="A45" t="s">
         <v>4</v>
       </c>
-      <c r="B45">
-        <v>2021</v>
+      <c r="B45" s="3">
+        <v>44197</v>
       </c>
       <c r="C45" s="1">
         <v>93.6</v>
@@ -1491,8 +1493,8 @@
       <c r="A46" t="s">
         <v>4</v>
       </c>
-      <c r="B46">
-        <v>2022</v>
+      <c r="B46" s="3">
+        <v>44562</v>
       </c>
       <c r="C46" s="1">
         <v>93.733333333333348</v>
@@ -1513,8 +1515,8 @@
       <c r="A47" t="s">
         <v>5</v>
       </c>
-      <c r="B47">
-        <v>2014</v>
+      <c r="B47" s="3">
+        <v>41640</v>
       </c>
       <c r="C47" s="1">
         <v>60.7</v>
@@ -1535,8 +1537,8 @@
       <c r="A48" t="s">
         <v>5</v>
       </c>
-      <c r="B48">
-        <v>2015</v>
+      <c r="B48" s="3">
+        <v>42005</v>
       </c>
       <c r="C48" s="1">
         <v>62.1</v>
@@ -1557,8 +1559,8 @@
       <c r="A49" t="s">
         <v>5</v>
       </c>
-      <c r="B49">
-        <v>2016</v>
+      <c r="B49" s="3">
+        <v>42370</v>
       </c>
       <c r="C49" s="1">
         <v>63.1</v>
@@ -1579,8 +1581,8 @@
       <c r="A50" t="s">
         <v>5</v>
       </c>
-      <c r="B50">
-        <v>2017</v>
+      <c r="B50" s="3">
+        <v>42736</v>
       </c>
       <c r="C50" s="1">
         <v>64.7</v>
@@ -1601,8 +1603,8 @@
       <c r="A51" t="s">
         <v>5</v>
       </c>
-      <c r="B51">
-        <v>2018</v>
+      <c r="B51" s="3">
+        <v>43101</v>
       </c>
       <c r="C51" s="1">
         <v>68</v>
@@ -1623,8 +1625,8 @@
       <c r="A52" t="s">
         <v>5</v>
       </c>
-      <c r="B52">
-        <v>2019</v>
+      <c r="B52" s="3">
+        <v>43466</v>
       </c>
       <c r="C52" s="1">
         <v>69.3</v>
@@ -1645,8 +1647,8 @@
       <c r="A53" t="s">
         <v>5</v>
       </c>
-      <c r="B53">
-        <v>2020</v>
+      <c r="B53" s="3">
+        <v>43831</v>
       </c>
       <c r="C53" s="1">
         <v>69.3</v>
@@ -1667,8 +1669,8 @@
       <c r="A54" t="s">
         <v>5</v>
       </c>
-      <c r="B54">
-        <v>2021</v>
+      <c r="B54" s="3">
+        <v>44197</v>
       </c>
       <c r="C54" s="1">
         <v>71.900000000000006</v>
@@ -1689,8 +1691,8 @@
       <c r="A55" t="s">
         <v>5</v>
       </c>
-      <c r="B55">
-        <v>2022</v>
+      <c r="B55" s="3">
+        <v>44562</v>
       </c>
       <c r="C55" s="1">
         <v>70.166666666666671</v>
@@ -1711,8 +1713,8 @@
       <c r="A56" t="s">
         <v>6</v>
       </c>
-      <c r="B56">
-        <v>2014</v>
+      <c r="B56" s="3">
+        <v>41640</v>
       </c>
       <c r="C56" s="1">
         <v>144.30000000000001</v>
@@ -1733,8 +1735,8 @@
       <c r="A57" t="s">
         <v>6</v>
       </c>
-      <c r="B57">
-        <v>2015</v>
+      <c r="B57" s="3">
+        <v>42005</v>
       </c>
       <c r="C57" s="1">
         <v>143.6</v>
@@ -1755,8 +1757,8 @@
       <c r="A58" t="s">
         <v>6</v>
       </c>
-      <c r="B58">
-        <v>2016</v>
+      <c r="B58" s="3">
+        <v>42370</v>
       </c>
       <c r="C58" s="1">
         <v>146.1</v>
@@ -1777,8 +1779,8 @@
       <c r="A59" t="s">
         <v>6</v>
       </c>
-      <c r="B59">
-        <v>2017</v>
+      <c r="B59" s="3">
+        <v>42736</v>
       </c>
       <c r="C59" s="1">
         <v>143.4</v>
@@ -1799,8 +1801,8 @@
       <c r="A60" t="s">
         <v>6</v>
       </c>
-      <c r="B60">
-        <v>2018</v>
+      <c r="B60" s="3">
+        <v>43101</v>
       </c>
       <c r="C60" s="1">
         <v>142.4</v>
@@ -1821,8 +1823,8 @@
       <c r="A61" t="s">
         <v>6</v>
       </c>
-      <c r="B61">
-        <v>2019</v>
+      <c r="B61" s="3">
+        <v>43466</v>
       </c>
       <c r="C61" s="1">
         <v>143.6</v>
@@ -1843,8 +1845,8 @@
       <c r="A62" t="s">
         <v>6</v>
       </c>
-      <c r="B62">
-        <v>2020</v>
+      <c r="B62" s="3">
+        <v>43831</v>
       </c>
       <c r="C62" s="1">
         <v>143.69999999999999</v>
@@ -1865,8 +1867,8 @@
       <c r="A63" t="s">
         <v>6</v>
       </c>
-      <c r="B63">
-        <v>2021</v>
+      <c r="B63" s="3">
+        <v>44197</v>
       </c>
       <c r="C63" s="1">
         <v>143.9</v>
@@ -1887,8 +1889,8 @@
       <c r="A64" t="s">
         <v>6</v>
       </c>
-      <c r="B64">
-        <v>2022</v>
+      <c r="B64" s="3">
+        <v>44562</v>
       </c>
       <c r="C64" s="1">
         <v>143.73333333333332</v>
@@ -1909,8 +1911,8 @@
       <c r="A65" t="s">
         <v>7</v>
       </c>
-      <c r="B65">
-        <v>2014</v>
+      <c r="B65" s="3">
+        <v>41640</v>
       </c>
       <c r="C65" s="1">
         <v>72.8</v>
@@ -1931,8 +1933,8 @@
       <c r="A66" t="s">
         <v>7</v>
       </c>
-      <c r="B66">
-        <v>2015</v>
+      <c r="B66" s="3">
+        <v>42005</v>
       </c>
       <c r="C66" s="1">
         <v>73.3</v>
@@ -1953,8 +1955,8 @@
       <c r="A67" t="s">
         <v>7</v>
       </c>
-      <c r="B67">
-        <v>2016</v>
+      <c r="B67" s="3">
+        <v>42370</v>
       </c>
       <c r="C67" s="1">
         <v>74.599999999999994</v>
@@ -1975,8 +1977,8 @@
       <c r="A68" t="s">
         <v>7</v>
       </c>
-      <c r="B68">
-        <v>2017</v>
+      <c r="B68" s="3">
+        <v>42736</v>
       </c>
       <c r="C68" s="1">
         <v>77</v>
@@ -1997,8 +1999,8 @@
       <c r="A69" t="s">
         <v>7</v>
       </c>
-      <c r="B69">
-        <v>2018</v>
+      <c r="B69" s="3">
+        <v>43101</v>
       </c>
       <c r="C69" s="1">
         <v>79.599999999999994</v>
@@ -2019,8 +2021,8 @@
       <c r="A70" t="s">
         <v>7</v>
       </c>
-      <c r="B70">
-        <v>2019</v>
+      <c r="B70" s="3">
+        <v>43466</v>
       </c>
       <c r="C70" s="1">
         <v>82</v>
@@ -2041,8 +2043,8 @@
       <c r="A71" t="s">
         <v>7</v>
       </c>
-      <c r="B71">
-        <v>2020</v>
+      <c r="B71" s="3">
+        <v>43831</v>
       </c>
       <c r="C71" s="1">
         <v>81.400000000000006</v>
@@ -2063,8 +2065,8 @@
       <c r="A72" t="s">
         <v>7</v>
       </c>
-      <c r="B72">
-        <v>2021</v>
+      <c r="B72" s="3">
+        <v>44197</v>
       </c>
       <c r="C72" s="1">
         <v>83.6</v>
@@ -2085,8 +2087,8 @@
       <c r="A73" t="s">
         <v>7</v>
       </c>
-      <c r="B73">
-        <v>2022</v>
+      <c r="B73" s="3">
+        <v>44562</v>
       </c>
       <c r="C73" s="1">
         <v>82.333333333333329</v>
@@ -2107,8 +2109,8 @@
       <c r="A74" t="s">
         <v>8</v>
       </c>
-      <c r="B74">
-        <v>2014</v>
+      <c r="B74" s="3">
+        <v>41640</v>
       </c>
       <c r="C74" s="1">
         <v>128</v>
@@ -2129,8 +2131,8 @@
       <c r="A75" t="s">
         <v>8</v>
       </c>
-      <c r="B75">
-        <v>2015</v>
+      <c r="B75" s="3">
+        <v>42005</v>
       </c>
       <c r="C75" s="1">
         <v>127.3</v>
@@ -2151,8 +2153,8 @@
       <c r="A76" t="s">
         <v>8</v>
       </c>
-      <c r="B76">
-        <v>2016</v>
+      <c r="B76" s="3">
+        <v>42370</v>
       </c>
       <c r="C76" s="1">
         <v>127.8</v>
@@ -2173,8 +2175,8 @@
       <c r="A77" t="s">
         <v>8</v>
       </c>
-      <c r="B77">
-        <v>2017</v>
+      <c r="B77" s="3">
+        <v>42736</v>
       </c>
       <c r="C77" s="1">
         <v>126.3</v>
@@ -2195,8 +2197,8 @@
       <c r="A78" t="s">
         <v>8</v>
       </c>
-      <c r="B78">
-        <v>2018</v>
+      <c r="B78" s="3">
+        <v>43101</v>
       </c>
       <c r="C78" s="1">
         <v>126.7</v>
@@ -2217,8 +2219,8 @@
       <c r="A79" t="s">
         <v>8</v>
       </c>
-      <c r="B79">
-        <v>2019</v>
+      <c r="B79" s="3">
+        <v>43466</v>
       </c>
       <c r="C79" s="1">
         <v>128.5</v>
@@ -2239,8 +2241,8 @@
       <c r="A80" t="s">
         <v>8</v>
       </c>
-      <c r="B80">
-        <v>2020</v>
+      <c r="B80" s="3">
+        <v>43831</v>
       </c>
       <c r="C80" s="1">
         <v>128.30000000000001</v>
@@ -2261,8 +2263,8 @@
       <c r="A81" t="s">
         <v>8</v>
       </c>
-      <c r="B81">
-        <v>2021</v>
+      <c r="B81" s="3">
+        <v>44197</v>
       </c>
       <c r="C81" s="1">
         <v>129.30000000000001</v>
@@ -2283,8 +2285,8 @@
       <c r="A82" t="s">
         <v>8</v>
       </c>
-      <c r="B82">
-        <v>2022</v>
+      <c r="B82" s="3">
+        <v>44562</v>
       </c>
       <c r="C82" s="1">
         <v>128.70000000000002</v>
@@ -2305,8 +2307,8 @@
       <c r="A83" t="s">
         <v>9</v>
       </c>
-      <c r="B83">
-        <v>2014</v>
+      <c r="B83" s="3">
+        <v>41640</v>
       </c>
       <c r="C83" s="1">
         <v>110.5</v>
@@ -2327,8 +2329,8 @@
       <c r="A84" t="s">
         <v>9</v>
       </c>
-      <c r="B84">
-        <v>2015</v>
+      <c r="B84" s="3">
+        <v>42005</v>
       </c>
       <c r="C84" s="1">
         <v>110.6</v>
@@ -2349,8 +2351,8 @@
       <c r="A85" t="s">
         <v>9</v>
       </c>
-      <c r="B85">
-        <v>2016</v>
+      <c r="B85" s="3">
+        <v>42370</v>
       </c>
       <c r="C85" s="1">
         <v>110.2</v>
@@ -2371,8 +2373,8 @@
       <c r="A86" t="s">
         <v>9</v>
       </c>
-      <c r="B86">
-        <v>2017</v>
+      <c r="B86" s="3">
+        <v>42736</v>
       </c>
       <c r="C86" s="1">
         <v>110.6</v>
@@ -2393,8 +2395,8 @@
       <c r="A87" t="s">
         <v>9</v>
       </c>
-      <c r="B87">
-        <v>2018</v>
+      <c r="B87" s="3">
+        <v>43101</v>
       </c>
       <c r="C87" s="1">
         <v>111</v>
@@ -2415,8 +2417,8 @@
       <c r="A88" t="s">
         <v>9</v>
       </c>
-      <c r="B88">
-        <v>2019</v>
+      <c r="B88" s="3">
+        <v>43466</v>
       </c>
       <c r="C88" s="1">
         <v>109.7</v>
@@ -2437,8 +2439,8 @@
       <c r="A89" t="s">
         <v>9</v>
       </c>
-      <c r="B89">
-        <v>2020</v>
+      <c r="B89" s="3">
+        <v>43831</v>
       </c>
       <c r="C89" s="1">
         <v>108.8</v>
@@ -2459,8 +2461,8 @@
       <c r="A90" t="s">
         <v>9</v>
       </c>
-      <c r="B90">
-        <v>2021</v>
+      <c r="B90" s="3">
+        <v>44197</v>
       </c>
       <c r="C90" s="1">
         <v>108.1</v>
@@ -2481,8 +2483,8 @@
       <c r="A91" t="s">
         <v>9</v>
       </c>
-      <c r="B91">
-        <v>2022</v>
+      <c r="B91" s="3">
+        <v>44562</v>
       </c>
       <c r="C91" s="1">
         <v>108.86666666666667</v>
@@ -2503,8 +2505,8 @@
       <c r="A92" t="s">
         <v>10</v>
       </c>
-      <c r="B92">
-        <v>2014</v>
+      <c r="B92" s="3">
+        <v>41640</v>
       </c>
       <c r="C92" s="1">
         <v>105.7</v>
@@ -2525,8 +2527,8 @@
       <c r="A93" t="s">
         <v>10</v>
       </c>
-      <c r="B93">
-        <v>2015</v>
+      <c r="B93" s="3">
+        <v>42005</v>
       </c>
       <c r="C93" s="1">
         <v>106.8</v>
@@ -2547,8 +2549,8 @@
       <c r="A94" t="s">
         <v>10</v>
       </c>
-      <c r="B94">
-        <v>2016</v>
+      <c r="B94" s="3">
+        <v>42370</v>
       </c>
       <c r="C94" s="1">
         <v>106.6</v>
@@ -2569,8 +2571,8 @@
       <c r="A95" t="s">
         <v>10</v>
       </c>
-      <c r="B95">
-        <v>2017</v>
+      <c r="B95" s="3">
+        <v>42736</v>
       </c>
       <c r="C95" s="1">
         <v>106.5</v>
@@ -2591,8 +2593,8 @@
       <c r="A96" t="s">
         <v>10</v>
       </c>
-      <c r="B96">
-        <v>2018</v>
+      <c r="B96" s="3">
+        <v>43101</v>
       </c>
       <c r="C96" s="1">
         <v>106.2</v>
@@ -2613,8 +2615,8 @@
       <c r="A97" t="s">
         <v>10</v>
       </c>
-      <c r="B97">
-        <v>2019</v>
+      <c r="B97" s="3">
+        <v>43466</v>
       </c>
       <c r="C97" s="1">
         <v>107.7</v>
@@ -2635,8 +2637,8 @@
       <c r="A98" t="s">
         <v>10</v>
       </c>
-      <c r="B98">
-        <v>2020</v>
+      <c r="B98" s="3">
+        <v>43831</v>
       </c>
       <c r="C98" s="1">
         <v>107.9</v>
@@ -2657,8 +2659,8 @@
       <c r="A99" t="s">
         <v>10</v>
       </c>
-      <c r="B99">
-        <v>2021</v>
+      <c r="B99" s="3">
+        <v>44197</v>
       </c>
       <c r="C99" s="1">
         <v>108.5</v>
@@ -2679,8 +2681,8 @@
       <c r="A100" t="s">
         <v>10</v>
       </c>
-      <c r="B100">
-        <v>2022</v>
+      <c r="B100" s="3">
+        <v>44562</v>
       </c>
       <c r="C100" s="1">
         <v>108.03333333333335</v>
@@ -2701,8 +2703,8 @@
       <c r="A101" t="s">
         <v>11</v>
       </c>
-      <c r="B101">
-        <v>2014</v>
+      <c r="B101" s="3">
+        <v>41640</v>
       </c>
       <c r="C101" s="1">
         <v>87.3</v>
@@ -2723,8 +2725,8 @@
       <c r="A102" t="s">
         <v>11</v>
       </c>
-      <c r="B102">
-        <v>2015</v>
+      <c r="B102" s="3">
+        <v>42005</v>
       </c>
       <c r="C102" s="1">
         <v>86.2</v>
@@ -2745,8 +2747,8 @@
       <c r="A103" t="s">
         <v>11</v>
       </c>
-      <c r="B103">
-        <v>2016</v>
+      <c r="B103" s="3">
+        <v>42370</v>
       </c>
       <c r="C103" s="1">
         <v>85.6</v>
@@ -2767,8 +2769,8 @@
       <c r="A104" t="s">
         <v>11</v>
       </c>
-      <c r="B104">
-        <v>2017</v>
+      <c r="B104" s="3">
+        <v>42736</v>
       </c>
       <c r="C104" s="1">
         <v>84.4</v>
@@ -2789,8 +2791,8 @@
       <c r="A105" t="s">
         <v>11</v>
       </c>
-      <c r="B105">
-        <v>2018</v>
+      <c r="B105" s="3">
+        <v>43101</v>
       </c>
       <c r="C105" s="1">
         <v>84.2</v>
@@ -2811,8 +2813,8 @@
       <c r="A106" t="s">
         <v>11</v>
       </c>
-      <c r="B106">
-        <v>2019</v>
+      <c r="B106" s="3">
+        <v>43466</v>
       </c>
       <c r="C106" s="1">
         <v>84.9</v>
@@ -2833,8 +2835,8 @@
       <c r="A107" t="s">
         <v>11</v>
       </c>
-      <c r="B107">
-        <v>2020</v>
+      <c r="B107" s="3">
+        <v>43831</v>
       </c>
       <c r="C107" s="1">
         <v>85.2</v>
@@ -2855,8 +2857,8 @@
       <c r="A108" t="s">
         <v>11</v>
       </c>
-      <c r="B108">
-        <v>2021</v>
+      <c r="B108" s="3">
+        <v>44197</v>
       </c>
       <c r="C108" s="1">
         <v>84.1</v>
@@ -2877,8 +2879,8 @@
       <c r="A109" t="s">
         <v>11</v>
       </c>
-      <c r="B109">
-        <v>2022</v>
+      <c r="B109" s="3">
+        <v>44562</v>
       </c>
       <c r="C109" s="1">
         <v>84.733333333333334</v>
@@ -2899,8 +2901,8 @@
       <c r="A110" t="s">
         <v>12</v>
       </c>
-      <c r="B110">
-        <v>2014</v>
+      <c r="B110" s="3">
+        <v>41640</v>
       </c>
       <c r="C110" s="1">
         <v>55.7</v>
@@ -2921,8 +2923,8 @@
       <c r="A111" t="s">
         <v>12</v>
       </c>
-      <c r="B111">
-        <v>2015</v>
+      <c r="B111" s="3">
+        <v>42005</v>
       </c>
       <c r="C111" s="1">
         <v>56.7</v>
@@ -2943,8 +2945,8 @@
       <c r="A112" t="s">
         <v>12</v>
       </c>
-      <c r="B112">
-        <v>2016</v>
+      <c r="B112" s="3">
+        <v>42370</v>
       </c>
       <c r="C112" s="1">
         <v>58.5</v>
@@ -2965,8 +2967,8 @@
       <c r="A113" t="s">
         <v>12</v>
       </c>
-      <c r="B113">
-        <v>2017</v>
+      <c r="B113" s="3">
+        <v>42736</v>
       </c>
       <c r="C113" s="1">
         <v>62.2</v>
@@ -2987,8 +2989,8 @@
       <c r="A114" t="s">
         <v>12</v>
       </c>
-      <c r="B114">
-        <v>2018</v>
+      <c r="B114" s="3">
+        <v>43101</v>
       </c>
       <c r="C114" s="1">
         <v>62.3</v>
@@ -3009,8 +3011,8 @@
       <c r="A115" t="s">
         <v>12</v>
       </c>
-      <c r="B115">
-        <v>2019</v>
+      <c r="B115" s="3">
+        <v>43466</v>
       </c>
       <c r="C115" s="1">
         <v>63.6</v>
@@ -3031,8 +3033,8 @@
       <c r="A116" t="s">
         <v>12</v>
       </c>
-      <c r="B116">
-        <v>2020</v>
+      <c r="B116" s="3">
+        <v>43831</v>
       </c>
       <c r="C116" s="1">
         <v>61</v>
@@ -3053,8 +3055,8 @@
       <c r="A117" t="s">
         <v>12</v>
       </c>
-      <c r="B117">
-        <v>2021</v>
+      <c r="B117" s="3">
+        <v>44197</v>
       </c>
       <c r="C117" s="1">
         <v>62.7</v>
@@ -3075,8 +3077,8 @@
       <c r="A118" t="s">
         <v>12</v>
       </c>
-      <c r="B118">
-        <v>2022</v>
+      <c r="B118" s="3">
+        <v>44562</v>
       </c>
       <c r="C118" s="1">
         <v>62.433333333333337</v>
@@ -3097,8 +3099,8 @@
       <c r="A119" t="s">
         <v>13</v>
       </c>
-      <c r="B119">
-        <v>2014</v>
+      <c r="B119" s="3">
+        <v>41640</v>
       </c>
       <c r="C119" s="1">
         <v>130.1</v>
@@ -3119,8 +3121,8 @@
       <c r="A120" t="s">
         <v>13</v>
       </c>
-      <c r="B120">
-        <v>2015</v>
+      <c r="B120" s="3">
+        <v>42005</v>
       </c>
       <c r="C120" s="1">
         <v>130</v>
@@ -3141,8 +3143,8 @@
       <c r="A121" t="s">
         <v>13</v>
       </c>
-      <c r="B121">
-        <v>2016</v>
+      <c r="B121" s="3">
+        <v>42370</v>
       </c>
       <c r="C121" s="1">
         <v>131.69999999999999</v>
@@ -3163,8 +3165,8 @@
       <c r="A122" t="s">
         <v>13</v>
       </c>
-      <c r="B122">
-        <v>2017</v>
+      <c r="B122" s="3">
+        <v>42736</v>
       </c>
       <c r="C122" s="1">
         <v>133.9</v>
@@ -3185,8 +3187,8 @@
       <c r="A123" t="s">
         <v>13</v>
       </c>
-      <c r="B123">
-        <v>2018</v>
+      <c r="B123" s="3">
+        <v>43101</v>
       </c>
       <c r="C123" s="1">
         <v>135.69999999999999</v>
@@ -3207,8 +3209,8 @@
       <c r="A124" t="s">
         <v>13</v>
       </c>
-      <c r="B124">
-        <v>2019</v>
+      <c r="B124" s="3">
+        <v>43466</v>
       </c>
       <c r="C124" s="1">
         <v>139</v>
@@ -3229,8 +3231,8 @@
       <c r="A125" t="s">
         <v>13</v>
       </c>
-      <c r="B125">
-        <v>2020</v>
+      <c r="B125" s="3">
+        <v>43831</v>
       </c>
       <c r="C125" s="1">
         <v>145.19999999999999</v>
@@ -3251,8 +3253,8 @@
       <c r="A126" t="s">
         <v>13</v>
       </c>
-      <c r="B126">
-        <v>2021</v>
+      <c r="B126" s="3">
+        <v>44197</v>
       </c>
       <c r="C126" s="1">
         <v>146.4</v>
@@ -3273,8 +3275,8 @@
       <c r="A127" t="s">
         <v>13</v>
       </c>
-      <c r="B127">
-        <v>2022</v>
+      <c r="B127" s="3">
+        <v>44562</v>
       </c>
       <c r="C127" s="1">
         <v>143.53333333333333</v>
@@ -3295,8 +3297,8 @@
       <c r="A128" t="s">
         <v>14</v>
       </c>
-      <c r="B128">
-        <v>2014</v>
+      <c r="B128" s="3">
+        <v>41640</v>
       </c>
       <c r="C128" s="1">
         <v>106.9</v>
@@ -3317,8 +3319,8 @@
       <c r="A129" t="s">
         <v>14</v>
       </c>
-      <c r="B129">
-        <v>2015</v>
+      <c r="B129" s="3">
+        <v>42005</v>
       </c>
       <c r="C129" s="1">
         <v>106.7</v>
@@ -3339,8 +3341,8 @@
       <c r="A130" t="s">
         <v>14</v>
       </c>
-      <c r="B130">
-        <v>2016</v>
+      <c r="B130" s="3">
+        <v>42370</v>
       </c>
       <c r="C130" s="1">
         <v>105.3</v>
@@ -3361,8 +3363,8 @@
       <c r="A131" t="s">
         <v>14</v>
       </c>
-      <c r="B131">
-        <v>2017</v>
+      <c r="B131" s="3">
+        <v>42736</v>
       </c>
       <c r="C131" s="1">
         <v>104.7</v>
@@ -3383,8 +3385,8 @@
       <c r="A132" t="s">
         <v>14</v>
       </c>
-      <c r="B132">
-        <v>2018</v>
+      <c r="B132" s="3">
+        <v>43101</v>
       </c>
       <c r="C132" s="1">
         <v>104.4</v>
@@ -3405,8 +3407,8 @@
       <c r="A133" t="s">
         <v>14</v>
       </c>
-      <c r="B133">
-        <v>2019</v>
+      <c r="B133" s="3">
+        <v>43466</v>
       </c>
       <c r="C133" s="1">
         <v>103</v>
@@ -3427,8 +3429,8 @@
       <c r="A134" t="s">
         <v>14</v>
       </c>
-      <c r="B134">
-        <v>2020</v>
+      <c r="B134" s="3">
+        <v>43831</v>
       </c>
       <c r="C134" s="1">
         <v>102.5</v>
@@ -3449,8 +3451,8 @@
       <c r="A135" t="s">
         <v>14</v>
       </c>
-      <c r="B135">
-        <v>2021</v>
+      <c r="B135" s="3">
+        <v>44197</v>
       </c>
       <c r="C135" s="1">
         <v>101.6</v>
@@ -3471,8 +3473,8 @@
       <c r="A136" t="s">
         <v>14</v>
       </c>
-      <c r="B136">
-        <v>2022</v>
+      <c r="B136" s="3">
+        <v>44562</v>
       </c>
       <c r="C136" s="1">
         <v>102.36666666666667</v>
@@ -3493,8 +3495,8 @@
       <c r="A137" t="s">
         <v>15</v>
       </c>
-      <c r="B137">
-        <v>2014</v>
+      <c r="B137" s="3">
+        <v>41640</v>
       </c>
       <c r="C137" s="1">
         <v>68.8</v>
@@ -3515,8 +3517,8 @@
       <c r="A138" t="s">
         <v>15</v>
       </c>
-      <c r="B138">
-        <v>2015</v>
+      <c r="B138" s="3">
+        <v>42005</v>
       </c>
       <c r="C138" s="1">
         <v>68.3</v>
@@ -3537,8 +3539,8 @@
       <c r="A139" t="s">
         <v>15</v>
       </c>
-      <c r="B139">
-        <v>2016</v>
+      <c r="B139" s="3">
+        <v>42370</v>
       </c>
       <c r="C139" s="1">
         <v>69.5</v>
@@ -3559,8 +3561,8 @@
       <c r="A140" t="s">
         <v>15</v>
       </c>
-      <c r="B140">
-        <v>2017</v>
+      <c r="B140" s="3">
+        <v>42736</v>
       </c>
       <c r="C140" s="1">
         <v>70.2</v>
@@ -3581,8 +3583,8 @@
       <c r="A141" t="s">
         <v>15</v>
       </c>
-      <c r="B141">
-        <v>2018</v>
+      <c r="B141" s="3">
+        <v>43101</v>
       </c>
       <c r="C141" s="1">
         <v>72.099999999999994</v>
@@ -3603,8 +3605,8 @@
       <c r="A142" t="s">
         <v>15</v>
       </c>
-      <c r="B142">
-        <v>2019</v>
+      <c r="B142" s="3">
+        <v>43466</v>
       </c>
       <c r="C142" s="1">
         <v>73.8</v>
@@ -3625,8 +3627,8 @@
       <c r="A143" t="s">
         <v>15</v>
       </c>
-      <c r="B143">
-        <v>2020</v>
+      <c r="B143" s="3">
+        <v>43831</v>
       </c>
       <c r="C143" s="1">
         <v>74.099999999999994</v>
@@ -3647,8 +3649,8 @@
       <c r="A144" t="s">
         <v>15</v>
       </c>
-      <c r="B144">
-        <v>2021</v>
+      <c r="B144" s="3">
+        <v>44197</v>
       </c>
       <c r="C144" s="1">
         <v>76.3</v>
@@ -3669,8 +3671,8 @@
       <c r="A145" t="s">
         <v>15</v>
       </c>
-      <c r="B145">
-        <v>2022</v>
+      <c r="B145" s="3">
+        <v>44562</v>
       </c>
       <c r="C145" s="1">
         <v>74.733333333333334</v>
@@ -3691,8 +3693,8 @@
       <c r="A146" t="s">
         <v>16</v>
       </c>
-      <c r="B146">
-        <v>2014</v>
+      <c r="B146" s="3">
+        <v>41640</v>
       </c>
       <c r="C146" s="1">
         <v>59.3</v>
@@ -3713,8 +3715,8 @@
       <c r="A147" t="s">
         <v>16</v>
       </c>
-      <c r="B147">
-        <v>2015</v>
+      <c r="B147" s="3">
+        <v>42005</v>
       </c>
       <c r="C147" s="1">
         <v>59.4</v>
@@ -3735,8 +3737,8 @@
       <c r="A148" t="s">
         <v>16</v>
       </c>
-      <c r="B148">
-        <v>2016</v>
+      <c r="B148" s="3">
+        <v>42370</v>
       </c>
       <c r="C148" s="1">
         <v>60.6</v>
@@ -3757,8 +3759,8 @@
       <c r="A149" t="s">
         <v>16</v>
       </c>
-      <c r="B149">
-        <v>2017</v>
+      <c r="B149" s="3">
+        <v>42736</v>
       </c>
       <c r="C149" s="1">
         <v>61.5</v>
@@ -3779,8 +3781,8 @@
       <c r="A150" t="s">
         <v>16</v>
       </c>
-      <c r="B150">
-        <v>2018</v>
+      <c r="B150" s="3">
+        <v>43101</v>
       </c>
       <c r="C150" s="1">
         <v>63.5</v>
@@ -3801,8 +3803,8 @@
       <c r="A151" t="s">
         <v>16</v>
       </c>
-      <c r="B151">
-        <v>2019</v>
+      <c r="B151" s="3">
+        <v>43466</v>
       </c>
       <c r="C151" s="1">
         <v>64.099999999999994</v>
@@ -3823,8 +3825,8 @@
       <c r="A152" t="s">
         <v>16</v>
       </c>
-      <c r="B152">
-        <v>2020</v>
+      <c r="B152" s="3">
+        <v>43831</v>
       </c>
       <c r="C152" s="1">
         <v>66</v>
@@ -3845,8 +3847,8 @@
       <c r="A153" t="s">
         <v>16</v>
       </c>
-      <c r="B153">
-        <v>2021</v>
+      <c r="B153" s="3">
+        <v>44197</v>
       </c>
       <c r="C153" s="1">
         <v>67.8</v>
@@ -3867,8 +3869,8 @@
       <c r="A154" t="s">
         <v>16</v>
       </c>
-      <c r="B154">
-        <v>2022</v>
+      <c r="B154" s="3">
+        <v>44562</v>
       </c>
       <c r="C154" s="1">
         <v>65.966666666666654</v>
@@ -3889,8 +3891,8 @@
       <c r="A155" t="s">
         <v>17</v>
       </c>
-      <c r="B155">
-        <v>2014</v>
+      <c r="B155" s="3">
+        <v>41640</v>
       </c>
       <c r="C155" s="1">
         <v>141.4</v>
@@ -3911,8 +3913,8 @@
       <c r="A156" t="s">
         <v>17</v>
       </c>
-      <c r="B156">
-        <v>2015</v>
+      <c r="B156" s="3">
+        <v>42005</v>
       </c>
       <c r="C156" s="1">
         <v>140.6</v>
@@ -3933,8 +3935,8 @@
       <c r="A157" t="s">
         <v>17</v>
       </c>
-      <c r="B157">
-        <v>2016</v>
+      <c r="B157" s="3">
+        <v>42370</v>
       </c>
       <c r="C157" s="1">
         <v>141.9</v>
@@ -3955,8 +3957,8 @@
       <c r="A158" t="s">
         <v>17</v>
       </c>
-      <c r="B158">
-        <v>2017</v>
+      <c r="B158" s="3">
+        <v>42736</v>
       </c>
       <c r="C158" s="1">
         <v>142.6</v>
@@ -3977,8 +3979,8 @@
       <c r="A159" t="s">
         <v>17</v>
       </c>
-      <c r="B159">
-        <v>2018</v>
+      <c r="B159" s="3">
+        <v>43101</v>
       </c>
       <c r="C159" s="1">
         <v>141.5</v>
@@ -3999,8 +4001,8 @@
       <c r="A160" t="s">
         <v>17</v>
       </c>
-      <c r="B160">
-        <v>2019</v>
+      <c r="B160" s="3">
+        <v>43466</v>
       </c>
       <c r="C160" s="1">
         <v>147.1</v>
@@ -4021,8 +4023,8 @@
       <c r="A161" t="s">
         <v>17</v>
       </c>
-      <c r="B161">
-        <v>2020</v>
+      <c r="B161" s="3">
+        <v>43831</v>
       </c>
       <c r="C161" s="1">
         <v>153.9</v>
@@ -4043,8 +4045,8 @@
       <c r="A162" t="s">
         <v>17</v>
       </c>
-      <c r="B162">
-        <v>2021</v>
+      <c r="B162" s="3">
+        <v>44197</v>
       </c>
       <c r="C162" s="1">
         <v>153.1</v>
@@ -4065,8 +4067,8 @@
       <c r="A163" t="s">
         <v>17</v>
       </c>
-      <c r="B163">
-        <v>2022</v>
+      <c r="B163" s="3">
+        <v>44562</v>
       </c>
       <c r="C163" s="1">
         <v>151.36666666666667</v>
@@ -4087,8 +4089,8 @@
       <c r="A164" t="s">
         <v>18</v>
       </c>
-      <c r="B164">
-        <v>2014</v>
+      <c r="B164" s="3">
+        <v>41640</v>
       </c>
       <c r="C164" s="1">
         <v>83.9</v>
@@ -4109,8 +4111,8 @@
       <c r="A165" t="s">
         <v>18</v>
       </c>
-      <c r="B165">
-        <v>2015</v>
+      <c r="B165" s="3">
+        <v>42005</v>
       </c>
       <c r="C165" s="1">
         <v>84.9</v>
@@ -4131,8 +4133,8 @@
       <c r="A166" t="s">
         <v>18</v>
       </c>
-      <c r="B166">
-        <v>2016</v>
+      <c r="B166" s="3">
+        <v>42370</v>
       </c>
       <c r="C166" s="1">
         <v>85</v>
@@ -4153,8 +4155,8 @@
       <c r="A167" t="s">
         <v>18</v>
       </c>
-      <c r="B167">
-        <v>2017</v>
+      <c r="B167" s="3">
+        <v>42736</v>
       </c>
       <c r="C167" s="1">
         <v>86.6</v>
@@ -4175,8 +4177,8 @@
       <c r="A168" t="s">
         <v>18</v>
       </c>
-      <c r="B168">
-        <v>2018</v>
+      <c r="B168" s="3">
+        <v>43101</v>
       </c>
       <c r="C168" s="1">
         <v>87</v>
@@ -4197,8 +4199,8 @@
       <c r="A169" t="s">
         <v>18</v>
       </c>
-      <c r="B169">
-        <v>2019</v>
+      <c r="B169" s="3">
+        <v>43466</v>
       </c>
       <c r="C169" s="1">
         <v>87.1</v>
@@ -4219,8 +4221,8 @@
       <c r="A170" t="s">
         <v>18</v>
       </c>
-      <c r="B170">
-        <v>2020</v>
+      <c r="B170" s="3">
+        <v>43831</v>
       </c>
       <c r="C170" s="1">
         <v>89.9</v>
@@ -4241,8 +4243,8 @@
       <c r="A171" t="s">
         <v>18</v>
       </c>
-      <c r="B171">
-        <v>2021</v>
+      <c r="B171" s="3">
+        <v>44197</v>
       </c>
       <c r="C171" s="1">
         <v>89.3</v>
@@ -4263,8 +4265,8 @@
       <c r="A172" t="s">
         <v>18</v>
       </c>
-      <c r="B172">
-        <v>2022</v>
+      <c r="B172" s="3">
+        <v>44562</v>
       </c>
       <c r="C172" s="1">
         <v>88.766666666666666</v>
@@ -4285,8 +4287,8 @@
       <c r="A173" t="s">
         <v>19</v>
       </c>
-      <c r="B173">
-        <v>2014</v>
+      <c r="B173" s="3">
+        <v>41640</v>
       </c>
       <c r="C173" s="1">
         <v>116.6</v>
@@ -4307,8 +4309,8 @@
       <c r="A174" t="s">
         <v>19</v>
       </c>
-      <c r="B174">
-        <v>2015</v>
+      <c r="B174" s="3">
+        <v>42005</v>
       </c>
       <c r="C174" s="1">
         <v>116.5</v>
@@ -4329,8 +4331,8 @@
       <c r="A175" t="s">
         <v>19</v>
       </c>
-      <c r="B175">
-        <v>2016</v>
+      <c r="B175" s="3">
+        <v>42370</v>
       </c>
       <c r="C175" s="1">
         <v>118.7</v>
@@ -4351,8 +4353,8 @@
       <c r="A176" t="s">
         <v>19</v>
       </c>
-      <c r="B176">
-        <v>2017</v>
+      <c r="B176" s="3">
+        <v>42736</v>
       </c>
       <c r="C176" s="1">
         <v>117.7</v>
@@ -4373,8 +4375,8 @@
       <c r="A177" t="s">
         <v>19</v>
       </c>
-      <c r="B177">
-        <v>2018</v>
+      <c r="B177" s="3">
+        <v>43101</v>
       </c>
       <c r="C177" s="1">
         <v>117.7</v>
@@ -4395,8 +4397,8 @@
       <c r="A178" t="s">
         <v>19</v>
       </c>
-      <c r="B178">
-        <v>2019</v>
+      <c r="B178" s="3">
+        <v>43466</v>
       </c>
       <c r="C178" s="1">
         <v>120.9</v>
@@ -4417,8 +4419,8 @@
       <c r="A179" t="s">
         <v>19</v>
       </c>
-      <c r="B179">
-        <v>2020</v>
+      <c r="B179" s="3">
+        <v>43831</v>
       </c>
       <c r="C179" s="1">
         <v>120</v>
@@ -4439,8 +4441,8 @@
       <c r="A180" t="s">
         <v>19</v>
       </c>
-      <c r="B180">
-        <v>2021</v>
+      <c r="B180" s="3">
+        <v>44197</v>
       </c>
       <c r="C180" s="1">
         <v>120.6</v>
@@ -4461,8 +4463,8 @@
       <c r="A181" t="s">
         <v>19</v>
       </c>
-      <c r="B181">
-        <v>2022</v>
+      <c r="B181" s="3">
+        <v>44562</v>
       </c>
       <c r="C181" s="1">
         <v>120.5</v>
@@ -4483,8 +4485,8 @@
       <c r="A182" t="s">
         <v>20</v>
       </c>
-      <c r="B182">
-        <v>2014</v>
+      <c r="B182" s="3">
+        <v>41640</v>
       </c>
       <c r="C182" s="1">
         <v>54.7</v>
@@ -4505,8 +4507,8 @@
       <c r="A183" t="s">
         <v>20</v>
       </c>
-      <c r="B183">
-        <v>2015</v>
+      <c r="B183" s="3">
+        <v>42005</v>
       </c>
       <c r="C183" s="1">
         <v>54.4</v>
@@ -4527,8 +4529,8 @@
       <c r="A184" t="s">
         <v>20</v>
       </c>
-      <c r="B184">
-        <v>2016</v>
+      <c r="B184" s="3">
+        <v>42370</v>
       </c>
       <c r="C184" s="1">
         <v>53</v>
@@ -4549,8 +4551,8 @@
       <c r="A185" t="s">
         <v>20</v>
       </c>
-      <c r="B185">
-        <v>2017</v>
+      <c r="B185" s="3">
+        <v>42736</v>
       </c>
       <c r="C185" s="1">
         <v>55.6</v>
@@ -4571,8 +4573,8 @@
       <c r="A186" t="s">
         <v>20</v>
       </c>
-      <c r="B186">
-        <v>2018</v>
+      <c r="B186" s="3">
+        <v>43101</v>
       </c>
       <c r="C186" s="1">
         <v>56.5</v>
@@ -4593,8 +4595,8 @@
       <c r="A187" t="s">
         <v>20</v>
       </c>
-      <c r="B187">
-        <v>2019</v>
+      <c r="B187" s="3">
+        <v>43466</v>
       </c>
       <c r="C187" s="1">
         <v>56.9</v>
@@ -4615,8 +4617,8 @@
       <c r="A188" t="s">
         <v>20</v>
       </c>
-      <c r="B188">
-        <v>2020</v>
+      <c r="B188" s="3">
+        <v>43831</v>
       </c>
       <c r="C188" s="1">
         <v>56</v>
@@ -4637,8 +4639,8 @@
       <c r="A189" t="s">
         <v>20</v>
       </c>
-      <c r="B189">
-        <v>2021</v>
+      <c r="B189" s="3">
+        <v>44197</v>
       </c>
       <c r="C189" s="1">
         <v>56.7</v>
@@ -4659,8 +4661,8 @@
       <c r="A190" t="s">
         <v>20</v>
       </c>
-      <c r="B190">
-        <v>2022</v>
+      <c r="B190" s="3">
+        <v>44562</v>
       </c>
       <c r="C190" s="1">
         <v>56.533333333333339</v>
@@ -4681,8 +4683,8 @@
       <c r="A191" t="s">
         <v>21</v>
       </c>
-      <c r="B191">
-        <v>2014</v>
+      <c r="B191" s="3">
+        <v>41640</v>
       </c>
       <c r="C191" s="1">
         <v>83.7</v>
@@ -4703,8 +4705,8 @@
       <c r="A192" t="s">
         <v>21</v>
       </c>
-      <c r="B192">
-        <v>2015</v>
+      <c r="B192" s="3">
+        <v>42005</v>
       </c>
       <c r="C192" s="1">
         <v>83.7</v>
@@ -4725,8 +4727,8 @@
       <c r="A193" t="s">
         <v>21</v>
       </c>
-      <c r="B193">
-        <v>2016</v>
+      <c r="B193" s="3">
+        <v>42370</v>
       </c>
       <c r="C193" s="1">
         <v>85.1</v>
@@ -4747,8 +4749,8 @@
       <c r="A194" t="s">
         <v>21</v>
       </c>
-      <c r="B194">
-        <v>2017</v>
+      <c r="B194" s="3">
+        <v>42736</v>
       </c>
       <c r="C194" s="1">
         <v>86.5</v>
@@ -4769,8 +4771,8 @@
       <c r="A195" t="s">
         <v>21</v>
       </c>
-      <c r="B195">
-        <v>2018</v>
+      <c r="B195" s="3">
+        <v>43101</v>
       </c>
       <c r="C195" s="1">
         <v>85.9</v>
@@ -4791,8 +4793,8 @@
       <c r="A196" t="s">
         <v>21</v>
       </c>
-      <c r="B196">
-        <v>2019</v>
+      <c r="B196" s="3">
+        <v>43466</v>
       </c>
       <c r="C196" s="1">
         <v>86.8</v>
@@ -4813,8 +4815,8 @@
       <c r="A197" t="s">
         <v>21</v>
       </c>
-      <c r="B197">
-        <v>2020</v>
+      <c r="B197" s="3">
+        <v>43831</v>
       </c>
       <c r="C197" s="1">
         <v>88.1</v>
@@ -4835,8 +4837,8 @@
       <c r="A198" t="s">
         <v>21</v>
       </c>
-      <c r="B198">
-        <v>2021</v>
+      <c r="B198" s="3">
+        <v>44197</v>
       </c>
       <c r="C198" s="1">
         <v>87.8</v>
@@ -4857,8 +4859,8 @@
       <c r="A199" t="s">
         <v>21</v>
       </c>
-      <c r="B199">
-        <v>2022</v>
+      <c r="B199" s="3">
+        <v>44562</v>
       </c>
       <c r="C199" s="1">
         <v>87.566666666666663</v>
@@ -4879,8 +4881,8 @@
       <c r="A200" t="s">
         <v>22</v>
       </c>
-      <c r="B200">
-        <v>2014</v>
+      <c r="B200" s="3">
+        <v>41640</v>
       </c>
       <c r="C200" s="1">
         <v>49.6</v>
@@ -4901,8 +4903,8 @@
       <c r="A201" t="s">
         <v>22</v>
       </c>
-      <c r="B201">
-        <v>2015</v>
+      <c r="B201" s="3">
+        <v>42005</v>
       </c>
       <c r="C201" s="1">
         <v>50.2</v>
@@ -4923,8 +4925,8 @@
       <c r="A202" t="s">
         <v>22</v>
       </c>
-      <c r="B202">
-        <v>2016</v>
+      <c r="B202" s="3">
+        <v>42370</v>
       </c>
       <c r="C202" s="1">
         <v>48.8</v>
@@ -4945,8 +4947,8 @@
       <c r="A203" t="s">
         <v>22</v>
       </c>
-      <c r="B203">
-        <v>2017</v>
+      <c r="B203" s="3">
+        <v>42736</v>
       </c>
       <c r="C203" s="1">
         <v>49.6</v>
@@ -4967,8 +4969,8 @@
       <c r="A204" t="s">
         <v>22</v>
       </c>
-      <c r="B204">
-        <v>2018</v>
+      <c r="B204" s="3">
+        <v>43101</v>
       </c>
       <c r="C204" s="1">
         <v>50.5</v>
@@ -4989,8 +4991,8 @@
       <c r="A205" t="s">
         <v>22</v>
       </c>
-      <c r="B205">
-        <v>2019</v>
+      <c r="B205" s="3">
+        <v>43466</v>
       </c>
       <c r="C205" s="1">
         <v>50.4</v>
@@ -5011,8 +5013,8 @@
       <c r="A206" t="s">
         <v>22</v>
       </c>
-      <c r="B206">
-        <v>2020</v>
+      <c r="B206" s="3">
+        <v>43831</v>
       </c>
       <c r="C206" s="1">
         <v>49.5</v>
@@ -5033,8 +5035,8 @@
       <c r="A207" t="s">
         <v>22</v>
       </c>
-      <c r="B207">
-        <v>2021</v>
+      <c r="B207" s="3">
+        <v>44197</v>
       </c>
       <c r="C207" s="1">
         <v>49.2</v>
@@ -5055,8 +5057,8 @@
       <c r="A208" t="s">
         <v>22</v>
       </c>
-      <c r="B208">
-        <v>2022</v>
+      <c r="B208" s="3">
+        <v>44562</v>
       </c>
       <c r="C208" s="1">
         <v>49.70000000000001</v>
@@ -5077,8 +5079,8 @@
       <c r="A209" t="s">
         <v>23</v>
       </c>
-      <c r="B209">
-        <v>2014</v>
+      <c r="B209" s="3">
+        <v>41640</v>
       </c>
       <c r="C209" s="1">
         <v>66</v>
@@ -5099,8 +5101,8 @@
       <c r="A210" t="s">
         <v>23</v>
       </c>
-      <c r="B210">
-        <v>2015</v>
+      <c r="B210" s="3">
+        <v>42005</v>
       </c>
       <c r="C210" s="1">
         <v>66.2</v>
@@ -5121,8 +5123,8 @@
       <c r="A211" t="s">
         <v>23</v>
       </c>
-      <c r="B211">
-        <v>2016</v>
+      <c r="B211" s="3">
+        <v>42370</v>
       </c>
       <c r="C211" s="1">
         <v>72.3</v>
@@ -5143,8 +5145,8 @@
       <c r="A212" t="s">
         <v>23</v>
       </c>
-      <c r="B212">
-        <v>2017</v>
+      <c r="B212" s="3">
+        <v>42736</v>
       </c>
       <c r="C212" s="1">
         <v>75.7</v>
@@ -5165,8 +5167,8 @@
       <c r="A213" t="s">
         <v>23</v>
       </c>
-      <c r="B213">
-        <v>2018</v>
+      <c r="B213" s="3">
+        <v>43101</v>
       </c>
       <c r="C213" s="1">
         <v>78.5</v>
@@ -5187,8 +5189,8 @@
       <c r="A214" t="s">
         <v>23</v>
       </c>
-      <c r="B214">
-        <v>2019</v>
+      <c r="B214" s="3">
+        <v>43466</v>
       </c>
       <c r="C214" s="1">
         <v>78.900000000000006</v>
@@ -5209,8 +5211,8 @@
       <c r="A215" t="s">
         <v>23</v>
       </c>
-      <c r="B215">
-        <v>2020</v>
+      <c r="B215" s="3">
+        <v>43831</v>
       </c>
       <c r="C215" s="1">
         <v>80.599999999999994</v>
@@ -5231,8 +5233,8 @@
       <c r="A216" t="s">
         <v>23</v>
       </c>
-      <c r="B216">
-        <v>2021</v>
+      <c r="B216" s="3">
+        <v>44197</v>
       </c>
       <c r="C216" s="1">
         <v>81.900000000000006</v>
@@ -5253,8 +5255,8 @@
       <c r="A217" t="s">
         <v>23</v>
       </c>
-      <c r="B217">
-        <v>2022</v>
+      <c r="B217" s="3">
+        <v>44562</v>
       </c>
       <c r="C217" s="1">
         <v>80.466666666666669</v>
@@ -5275,8 +5277,8 @@
       <c r="A218" t="s">
         <v>24</v>
       </c>
-      <c r="B218">
-        <v>2014</v>
+      <c r="B218" s="3">
+        <v>41640</v>
       </c>
       <c r="C218" s="1">
         <v>84.9</v>
@@ -5297,8 +5299,8 @@
       <c r="A219" t="s">
         <v>24</v>
       </c>
-      <c r="B219">
-        <v>2015</v>
+      <c r="B219" s="3">
+        <v>42005</v>
       </c>
       <c r="C219" s="1">
         <v>84.9</v>
@@ -5319,8 +5321,8 @@
       <c r="A220" t="s">
         <v>24</v>
       </c>
-      <c r="B220">
-        <v>2016</v>
+      <c r="B220" s="3">
+        <v>42370</v>
       </c>
       <c r="C220" s="1">
         <v>85.7</v>
@@ -5341,8 +5343,8 @@
       <c r="A221" t="s">
         <v>24</v>
       </c>
-      <c r="B221">
-        <v>2017</v>
+      <c r="B221" s="3">
+        <v>42736</v>
       </c>
       <c r="C221" s="1">
         <v>85.4</v>
@@ -5363,8 +5365,8 @@
       <c r="A222" t="s">
         <v>24</v>
       </c>
-      <c r="B222">
-        <v>2018</v>
+      <c r="B222" s="3">
+        <v>43101</v>
       </c>
       <c r="C222" s="1">
         <v>86.2</v>
@@ -5385,8 +5387,8 @@
       <c r="A223" t="s">
         <v>24</v>
       </c>
-      <c r="B223">
-        <v>2019</v>
+      <c r="B223" s="3">
+        <v>43466</v>
       </c>
       <c r="C223" s="1">
         <v>86.4</v>
@@ -5407,8 +5409,8 @@
       <c r="A224" t="s">
         <v>24</v>
       </c>
-      <c r="B224">
-        <v>2020</v>
+      <c r="B224" s="3">
+        <v>43831</v>
       </c>
       <c r="C224" s="1">
         <v>86.6</v>
@@ -5429,8 +5431,8 @@
       <c r="A225" t="s">
         <v>24</v>
       </c>
-      <c r="B225">
-        <v>2021</v>
+      <c r="B225" s="3">
+        <v>44197</v>
       </c>
       <c r="C225" s="1">
         <v>88.1</v>
@@ -5451,8 +5453,8 @@
       <c r="A226" t="s">
         <v>24</v>
       </c>
-      <c r="B226">
-        <v>2022</v>
+      <c r="B226" s="3">
+        <v>44562</v>
       </c>
       <c r="C226" s="1">
         <v>87.033333333333346</v>
@@ -5473,8 +5475,8 @@
       <c r="A227" t="s">
         <v>25</v>
       </c>
-      <c r="B227">
-        <v>2014</v>
+      <c r="B227" s="3">
+        <v>41640</v>
       </c>
       <c r="C227" s="1">
         <v>96.5</v>
@@ -5495,8 +5497,8 @@
       <c r="A228" t="s">
         <v>25</v>
       </c>
-      <c r="B228">
-        <v>2015</v>
+      <c r="B228" s="3">
+        <v>42005</v>
       </c>
       <c r="C228" s="1">
         <v>95.8</v>
@@ -5517,8 +5519,8 @@
       <c r="A229" t="s">
         <v>25</v>
       </c>
-      <c r="B229">
-        <v>2016</v>
+      <c r="B229" s="3">
+        <v>42370</v>
       </c>
       <c r="C229" s="1">
         <v>96.2</v>
@@ -5539,8 +5541,8 @@
       <c r="A230" t="s">
         <v>25</v>
       </c>
-      <c r="B230">
-        <v>2017</v>
+      <c r="B230" s="3">
+        <v>42736</v>
       </c>
       <c r="C230" s="1">
         <v>95.5</v>
@@ -5561,8 +5563,8 @@
       <c r="A231" t="s">
         <v>25</v>
       </c>
-      <c r="B231">
-        <v>2018</v>
+      <c r="B231" s="3">
+        <v>43101</v>
       </c>
       <c r="C231" s="1">
         <v>96.8</v>
@@ -5583,8 +5585,8 @@
       <c r="A232" t="s">
         <v>25</v>
       </c>
-      <c r="B232">
-        <v>2019</v>
+      <c r="B232" s="3">
+        <v>43466</v>
       </c>
       <c r="C232" s="1">
         <v>96.4</v>
@@ -5605,8 +5607,8 @@
       <c r="A233" t="s">
         <v>25</v>
       </c>
-      <c r="B233">
-        <v>2020</v>
+      <c r="B233" s="3">
+        <v>43831</v>
       </c>
       <c r="C233" s="1">
         <v>99.1</v>
@@ -5627,8 +5629,8 @@
       <c r="A234" t="s">
         <v>25</v>
       </c>
-      <c r="B234">
-        <v>2021</v>
+      <c r="B234" s="3">
+        <v>44197</v>
       </c>
       <c r="C234" s="1">
         <v>98.7</v>
@@ -5649,8 +5651,8 @@
       <c r="A235" t="s">
         <v>25</v>
       </c>
-      <c r="B235">
-        <v>2022</v>
+      <c r="B235" s="3">
+        <v>44562</v>
       </c>
       <c r="C235" s="1">
         <v>98.066666666666663</v>
@@ -5671,8 +5673,8 @@
       <c r="A236" t="s">
         <v>26</v>
       </c>
-      <c r="B236">
-        <v>2014</v>
+      <c r="B236" s="3">
+        <v>41640</v>
       </c>
       <c r="C236" s="1">
         <v>139.19999999999999</v>
@@ -5693,8 +5695,8 @@
       <c r="A237" t="s">
         <v>26</v>
       </c>
-      <c r="B237">
-        <v>2015</v>
+      <c r="B237" s="3">
+        <v>42005</v>
       </c>
       <c r="C237" s="1">
         <v>137</v>
@@ -5715,8 +5717,8 @@
       <c r="A238" t="s">
         <v>26</v>
       </c>
-      <c r="B238">
-        <v>2016</v>
+      <c r="B238" s="3">
+        <v>42370</v>
       </c>
       <c r="C238" s="1">
         <v>140.5</v>
@@ -5737,8 +5739,8 @@
       <c r="A239" t="s">
         <v>26</v>
       </c>
-      <c r="B239">
-        <v>2017</v>
+      <c r="B239" s="3">
+        <v>42736</v>
       </c>
       <c r="C239" s="1">
         <v>140.1</v>
@@ -5759,8 +5761,8 @@
       <c r="A240" t="s">
         <v>26</v>
       </c>
-      <c r="B240">
-        <v>2018</v>
+      <c r="B240" s="3">
+        <v>43101</v>
       </c>
       <c r="C240" s="1">
         <v>133.9</v>
@@ -5781,8 +5783,8 @@
       <c r="A241" t="s">
         <v>26</v>
       </c>
-      <c r="B241">
-        <v>2019</v>
+      <c r="B241" s="3">
+        <v>43466</v>
       </c>
       <c r="C241" s="1">
         <v>131.19999999999999</v>
@@ -5803,8 +5805,8 @@
       <c r="A242" t="s">
         <v>26</v>
       </c>
-      <c r="B242">
-        <v>2020</v>
+      <c r="B242" s="3">
+        <v>43831</v>
       </c>
       <c r="C242" s="1">
         <v>134.19999999999999</v>
@@ -5825,8 +5827,8 @@
       <c r="A243" t="s">
         <v>26</v>
       </c>
-      <c r="B243">
-        <v>2021</v>
+      <c r="B243" s="3">
+        <v>44197</v>
       </c>
       <c r="C243" s="1">
         <v>138.4</v>
@@ -5847,8 +5849,8 @@
       <c r="A244" t="s">
         <v>26</v>
       </c>
-      <c r="B244">
-        <v>2022</v>
+      <c r="B244" s="3">
+        <v>44562</v>
       </c>
       <c r="C244" s="1">
         <v>134.6</v>

--- a/Data/European Earnings Index.xlsx
+++ b/Data/European Earnings Index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\european-average-earnings-index\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4566196B-4094-4723-9455-599633B3F159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CAC288-5F32-4C33-B57B-29ED0CE6F487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="90" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="european_earnings_index" sheetId="1" r:id="rId1"/>
@@ -184,10 +184,10 @@
   </cellStyles>
   <dxfs count="4">
     <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
@@ -214,12 +214,12 @@
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{CB4AD6FB-72D6-498E-A9AD-12A465F0FBC2}" name="country"/>
     <tableColumn id="2" xr3:uid="{99E049E3-6CCE-4AFB-8FFC-0C279DC89557}" name="date"/>
-    <tableColumn id="3" xr3:uid="{4D95BB70-7F43-4895-B2D4-08D9A6AA4319}" name="price_level_index" dataDxfId="0"/>
-    <tableColumn id="6" xr3:uid="{7142205F-B21D-4A7A-8E0C-A302B67BB538}" name="annual_net_earnings" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{560F4622-03CE-4B2D-9B44-80296AFFDF06}" name="european_earnings_index" dataDxfId="2">
+    <tableColumn id="3" xr3:uid="{4D95BB70-7F43-4895-B2D4-08D9A6AA4319}" name="price_level_index" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{7142205F-B21D-4A7A-8E0C-A302B67BB538}" name="annual_net_earnings" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{560F4622-03CE-4B2D-9B44-80296AFFDF06}" name="european_earnings_index" dataDxfId="1">
       <calculatedColumnFormula>Table1[[#This Row],[annual_net_earnings]]*(1+(100-Table1[[#This Row],[price_level_index]])/100)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{D4D1ED1B-E2C5-4AB4-9F95-3A21FF9D2EB7}" name="yoy" dataDxfId="1">
+    <tableColumn id="9" xr3:uid="{D4D1ED1B-E2C5-4AB4-9F95-3A21FF9D2EB7}" name="yoy" dataDxfId="0">
       <calculatedColumnFormula>IF(B2&gt;B1,(Table1[[#This Row],[european_earnings_index]]-E1)/E1,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
